--- a/hk.xlsx
+++ b/hk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEI XIAO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25C45F4-2EA9-46A0-B414-4CE10594A080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDADB67-F405-4B08-A2BA-F5E701681F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28190,18 +28190,16 @@
   </si>
   <si>
     <t>商品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>条码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -28222,6 +28220,12 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFEF4343"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -28262,12 +28266,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -28592,10 +28597,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>9388</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>9389</v>
       </c>
       <c r="C1" s="2" t="s">

--- a/hk.xlsx
+++ b/hk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEI XIAO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDADB67-F405-4B08-A2BA-F5E701681F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A460C6F6-F376-4283-A148-4168CF22A4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28199,7 +28199,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -28214,18 +28214,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFEF4343"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -28266,13 +28254,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -28597,19 +28583,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>9388</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>9389</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>9385</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>9386</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>9387</v>
       </c>
     </row>

--- a/hk.xlsx
+++ b/hk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEI XIAO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A460C6F6-F376-4283-A148-4168CF22A4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1504CE63-61AD-4F7A-B4B0-755FF52371BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28189,10 +28189,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>商品名称</t>
-  </si>
-  <si>
-    <t>条码</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>barcode</t>
   </si>
 </sst>
 </file>
